--- a/收录曲目.xlsx
+++ b/收录曲目.xlsx
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10592700</v>
+        <v>10595482</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>8497379</v>
+        <v>8499662</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>7063935</v>
+        <v>7065033</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6841269</v>
+        <v>6843066</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6633250</v>
+        <v>6634606</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6180631</v>
+        <v>6181382</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6142939</v>
+        <v>6144278</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5655089</v>
+        <v>5656314</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5434044</v>
+        <v>5436669</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5426228</v>
+        <v>5427413</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>5411437</v>
+        <v>5413519</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>5231947</v>
+        <v>5239430</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5210623</v>
+        <v>5213303</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4902077</v>
+        <v>4902664</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4310870</v>
+        <v>4310955</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4290191</v>
+        <v>4291551</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>4190663</v>
+        <v>4194465</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4020423</v>
+        <v>4021829</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3942265</v>
+        <v>3943110</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3795821</v>
+        <v>3796535</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3790174</v>
+        <v>3791549</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3783752</v>
+        <v>3785023</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3679520</v>
+        <v>3681704</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3584936</v>
+        <v>3586024</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3550754</v>
+        <v>3552012</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3389941</v>
+        <v>3391269</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>3366022</v>
+        <v>3366296</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3324043</v>
+        <v>3324762</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3294653</v>
+        <v>3295734</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3272216</v>
+        <v>3273036</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3261397</v>
+        <v>3261989</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>3234637</v>
+        <v>3235778</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>3183376</v>
+        <v>3183981</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3178770</v>
+        <v>3179862</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3138741</v>
+        <v>3139265</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>3086993</v>
+        <v>3087287</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>3067846</v>
+        <v>3069361</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2949279</v>
+        <v>2950051</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2926545</v>
+        <v>2926846</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2925652</v>
+        <v>2926553</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2881031</v>
+        <v>2881551</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2874477</v>
+        <v>2875292</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2772396</v>
+        <v>2773214</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2704808</v>
+        <v>2705592</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2695950</v>
+        <v>2696342</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2655238</v>
+        <v>2655657</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2566015</v>
+        <v>2566840</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2526430</v>
+        <v>2526716</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2522514</v>
+        <v>2523071</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2489917</v>
+        <v>2490984</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2467054</v>
+        <v>2470989</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2457617</v>
+        <v>2457831</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2396302</v>
+        <v>2397074</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2392189</v>
+        <v>2392810</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2329005</v>
+        <v>2329237</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>2298753</v>
+        <v>2299197</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2298703</v>
+        <v>2299021</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>2276100</v>
+        <v>2276534</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2258914</v>
+        <v>2259361</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>2154379</v>
+        <v>2154670</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>2133006</v>
+        <v>2133431</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>2107097</v>
+        <v>2107594</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>2104825</v>
+        <v>2105707</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>2099622</v>
+        <v>2100541</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>2081206</v>
+        <v>2081977</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>2054172</v>
+        <v>2058036</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>2014892</v>
+        <v>2015190</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1992703</v>
+        <v>1993509</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1976017</v>
+        <v>1976414</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1938376</v>
+        <v>1938790</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1936758</v>
+        <v>1938081</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3171,77 +3171,77 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>太阳系迪斯科</t>
+          <t>混沌布吉</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BV1Fs411a7mr</t>
+          <t>BV1TP411Y7bt</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>【初音ミク】太阳系迪斯科【ナユタン星人】</t>
+          <t>混沌ブギ / jon-YAKITORY, 初音ミク -Konton Boogie / jon-YAKITORY, Hatsune Miku-</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1900019</v>
+        <v>1900832</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2017-01-20 20:22:58</t>
+          <t>2023-08-30 19:00:00</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>ナユタン星人</t>
+          <t>jon-YAKITORY</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>KitanoNani</t>
+          <t>jon_408</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>混沌布吉</t>
+          <t>太阳系迪斯科</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BV1TP411Y7bt</t>
+          <t>BV1Fs411a7mr</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>混沌ブギ / jon-YAKITORY, 初音ミク -Konton Boogie / jon-YAKITORY, Hatsune Miku-</t>
+          <t>【初音ミク】太阳系迪斯科【ナユタン星人】</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1897575</v>
+        <v>1900387</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2023-08-30 19:00:00</t>
+          <t>2017-01-20 20:22:58</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>jon-YAKITORY</t>
+          <t>ナユタン星人</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>jon_408</t>
+          <t>KitanoNani</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1888059</v>
+        <v>1888176</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1844279</v>
+        <v>1845118</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1834491</v>
+        <v>1834886</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1817320</v>
+        <v>1830948</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1816647</v>
+        <v>1825464</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1782629</v>
+        <v>1783142</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1777566</v>
+        <v>1778016</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1757523</v>
+        <v>1761198</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1748371</v>
+        <v>1748743</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1745506</v>
+        <v>1745873</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1736091</v>
+        <v>1736496</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1710095</v>
+        <v>1710401</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1694447</v>
+        <v>1694768</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1689610</v>
+        <v>1690037</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1671240</v>
+        <v>1671666</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1665163</v>
+        <v>1666630</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1661356</v>
+        <v>1662358</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1653584</v>
+        <v>1654097</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1631179</v>
+        <v>1631471</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1609933</v>
+        <v>1610295</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1604055</v>
+        <v>1604232</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1593553</v>
+        <v>1595627</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1567940</v>
+        <v>1568094</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1558842</v>
+        <v>1559431</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1528298</v>
+        <v>1528519</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1520143</v>
+        <v>1520774</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1504453</v>
+        <v>1504752</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1497154</v>
+        <v>1497279</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1494083</v>
+        <v>1494485</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -4349,77 +4349,77 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>明明曾爱着你</t>
+          <t>死别</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>BV1cx4y1X7qq</t>
+          <t>BV1oC411572T</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>【初音ミク】明明曾爱着你【MARETU】</t>
+          <t>MV「死別」 / Shannon feat. GUMI</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1481888</v>
+        <v>1489925</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2023-07-28 18:09:27</t>
+          <t>2024-03-29 19:00:00</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>MARETU</t>
+          <t>シャノン</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>KitanoNani</t>
+          <t>シャノン</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>死别</t>
+          <t>明明曾爱着你</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>BV1oC411572T</t>
+          <t>BV1cx4y1X7qq</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>MV「死別」 / Shannon feat. GUMI</t>
+          <t>【初音ミク】明明曾爱着你【MARETU】</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1480693</v>
+        <v>1482286</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2024-03-29 19:00:00</t>
+          <t>2023-07-28 18:09:27</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>シャノン</t>
+          <t>MARETU</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>シャノン</t>
+          <t>KitanoNani</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1469172</v>
+        <v>1469808</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1453709</v>
+        <v>1453929</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1444168</v>
+        <v>1444977</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1442846</v>
+        <v>1443793</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1440042</v>
+        <v>1440422</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1415031</v>
+        <v>1415224</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1403323</v>
+        <v>1407870</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1359328</v>
+        <v>1360041</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1334491</v>
+        <v>1336319</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1315583</v>
+        <v>1315826</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1302861</v>
+        <v>1303051</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1299345</v>
+        <v>1299762</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1282202</v>
+        <v>1282414</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1272868</v>
+        <v>1273037</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1220126</v>
+        <v>1220311</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1204033</v>
+        <v>1204250</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1197154</v>
+        <v>1197314</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1196086</v>
+        <v>1196313</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1188667</v>
+        <v>1191096</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1186689</v>
+        <v>1187029</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1184291</v>
+        <v>1184556</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1168778</v>
+        <v>1168998</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1143265</v>
+        <v>1143554</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1137409</v>
+        <v>1137810</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1128379</v>
+        <v>1131049</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1120407</v>
+        <v>1121909</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1115715</v>
+        <v>1116224</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1107666</v>
+        <v>1107854</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1100706</v>
+        <v>1100856</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1100071</v>
+        <v>1100334</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1094776</v>
+        <v>1095031</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1091394</v>
+        <v>1091630</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1090009</v>
+        <v>1090159</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1076839</v>
+        <v>1077753</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1076446</v>
+        <v>1077115</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1075832</v>
+        <v>1076225</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1051023</v>
+        <v>1051192</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1040691</v>
+        <v>1040882</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1014936</v>
+        <v>1015160</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1010156</v>
+        <v>1010642</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1001859</v>
+        <v>1001975</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1000414</v>
+        <v>1000708</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>992684</v>
+        <v>992863</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>978936</v>
+        <v>985986</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>969463</v>
+        <v>973037</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>967758</v>
+        <v>968268</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>956522</v>
+        <v>956716</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>948007</v>
+        <v>948163</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>945697</v>
+        <v>946062</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>929301</v>
+        <v>929466</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>927989</v>
+        <v>928129</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>920177</v>
+        <v>920628</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>908799</v>
+        <v>909044</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>887078</v>
+        <v>887445</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>882782</v>
+        <v>883040</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>879828</v>
+        <v>880071</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>878957</v>
+        <v>879252</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>872119</v>
+        <v>872240</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>870351</v>
+        <v>870667</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>863242</v>
+        <v>863571</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>862089</v>
+        <v>862196</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>847598</v>
+        <v>848964</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>836484</v>
+        <v>841273</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>835846</v>
+        <v>836370</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>830668</v>
+        <v>830740</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>813702</v>
+        <v>813884</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>808168</v>
+        <v>808276</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>800918</v>
+        <v>801314</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>795948</v>
+        <v>796036</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>791009</v>
+        <v>791067</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>757326</v>
+        <v>757642</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>750905</v>
+        <v>751223</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>749661</v>
+        <v>749814</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>747038</v>
+        <v>747434</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>745910</v>
+        <v>746062</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>728671</v>
+        <v>728836</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -7327,7 +7327,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>726046</v>
+        <v>726184</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>714602</v>
+        <v>714850</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>711424</v>
+        <v>712762</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>708097</v>
+        <v>708260</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>702445</v>
+        <v>703256</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>694760</v>
+        <v>694901</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>693318</v>
+        <v>693451</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>687090</v>
+        <v>687874</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>685053</v>
+        <v>685149</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>684403</v>
+        <v>684570</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>664792</v>
+        <v>665027</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>662123</v>
+        <v>662345</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>651944</v>
+        <v>652146</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>647312</v>
+        <v>647461</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>639520</v>
+        <v>639651</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>637391</v>
+        <v>637530</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>627173</v>
+        <v>627267</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>624460</v>
+        <v>625925</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>619460</v>
+        <v>619620</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>609635</v>
+        <v>609862</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -8087,7 +8087,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>606261</v>
+        <v>606883</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>604563</v>
+        <v>604762</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>583819</v>
+        <v>584663</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>571666</v>
+        <v>572278</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>561931</v>
+        <v>562179</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>542698</v>
+        <v>545490</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>539912</v>
+        <v>540049</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>537681</v>
+        <v>537834</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>528705</v>
+        <v>528867</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>511158</v>
+        <v>511256</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>504096</v>
+        <v>505741</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>486342</v>
+        <v>486701</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>481089</v>
+        <v>481447</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -8579,7 +8579,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>474425</v>
+        <v>475245</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>471847</v>
+        <v>471937</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>469991</v>
+        <v>470138</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>463504</v>
+        <v>463584</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>448847</v>
+        <v>449705</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>417970</v>
+        <v>419779</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>409740</v>
+        <v>409972</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>405510</v>
+        <v>406054</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>365286</v>
+        <v>365436</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>361913</v>
+        <v>361988</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>357822</v>
+        <v>358126</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>350824</v>
+        <v>350924</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>349522</v>
+        <v>349754</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>342993</v>
+        <v>343173</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -9111,7 +9111,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>338925</v>
+        <v>339315</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -9149,7 +9149,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>331559</v>
+        <v>331670</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>327450</v>
+        <v>327625</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>316725</v>
+        <v>317000</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>302360</v>
+        <v>302504</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -9301,7 +9301,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>301489</v>
+        <v>301799</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -9339,7 +9339,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>284476</v>
+        <v>285534</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>280228</v>
+        <v>280421</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>279474</v>
+        <v>279593</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>278623</v>
+        <v>278822</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>271209</v>
+        <v>271375</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>269570</v>
+        <v>269982</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>267435</v>
+        <v>267813</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>260457</v>
+        <v>260517</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>257168</v>
+        <v>260041</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -9667,35 +9667,35 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>深昏睡</t>
+          <t>超新星(雄之助)</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>BV1dx411s7po</t>
+          <t>BV1hw4m1e7Mm</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>春野 - 深昏睡／初音ミク</t>
+          <t>Supernova / 雄之助×春野 feat. 初音ミク【Music Video】</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>248483</v>
+        <v>248819</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2017-09-18 19:00:02</t>
+          <t>2024-06-20 18:01:24</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>春野</t>
+          <t>雄之助</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>春野xupxq_</t>
+          <t>雄之助</t>
         </is>
       </c>
       <c r="H244" t="n">
@@ -9705,35 +9705,35 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>石榴石之泪</t>
+          <t>深昏睡</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>BV1T34y1k7FL</t>
+          <t>BV1dx411s7po</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>【KAITO】ガーネットの涙/石榴石之泪【香椎モイミ】</t>
+          <t>春野 - 深昏睡／初音ミク</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>246370</v>
+        <v>248606</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2022-02-26 16:07:29</t>
+          <t>2017-09-18 19:00:02</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>香椎モイミ</t>
+          <t>春野</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>香椎モイミ</t>
+          <t>春野xupxq_</t>
         </is>
       </c>
       <c r="H245" t="n">
@@ -9743,35 +9743,35 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>超新星(雄之助)</t>
+          <t>石榴石之泪</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>BV1hw4m1e7Mm</t>
+          <t>BV1T34y1k7FL</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Supernova / 雄之助×春野 feat. 初音ミク【Music Video】</t>
+          <t>【KAITO】ガーネットの涙/石榴石之泪【香椎モイミ】</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>245807</v>
+        <v>246543</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2024-06-20 18:01:24</t>
+          <t>2022-02-26 16:07:29</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>雄之助</t>
+          <t>香椎モイミ</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>雄之助</t>
+          <t>香椎モイミ</t>
         </is>
       </c>
       <c r="H246" t="n">
@@ -9795,7 +9795,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>240859</v>
+        <v>240980</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>237866</v>
+        <v>238182</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -9871,7 +9871,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>237854</v>
+        <v>238025</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -9909,7 +9909,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>222865</v>
+        <v>223665</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
@@ -9933,77 +9933,77 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>就算你死了，我也会原谅你</t>
+          <t>喋喋不休吵死了</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>BV1Hy4y1d7to</t>
+          <t>BV13s41117kF</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Kikuo - 就算你死了，我也会原谅你 (君が死んでも許してあげるよ)</t>
+          <t>【亞北ネル】喋喋不休地吵死啦！【ガルナ@オワタP】</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>220147</v>
+        <v>220396</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2023-01-22 08:00:00</t>
+          <t>2016-07-20 19:37:25</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>kikuo</t>
+          <t>オワタP</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>kikuo_sound</t>
+          <t>゚下江小春</t>
         </is>
       </c>
       <c r="H251" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>喋喋不休吵死了</t>
+          <t>就算你死了，我也会原谅你</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>BV13s41117kF</t>
+          <t>BV1Hy4y1d7to</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>【亞北ネル】喋喋不休地吵死啦！【ガルナ@オワタP】</t>
+          <t>Kikuo - 就算你死了，我也会原谅你 (君が死んでも許してあげるよ)</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>220103</v>
+        <v>220169</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2016-07-20 19:37:25</t>
+          <t>2023-01-22 08:00:00</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>オワタP</t>
+          <t>kikuo</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>゚下江小春</t>
+          <t>kikuo_sound</t>
         </is>
       </c>
       <c r="H252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253">
@@ -10023,7 +10023,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>219547</v>
+        <v>219598</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
@@ -10061,7 +10061,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>218578</v>
+        <v>218623</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>218032</v>
+        <v>218083</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>217666</v>
+        <v>217707</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
@@ -10175,7 +10175,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>217443</v>
+        <v>217455</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>217412</v>
+        <v>217427</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>217103</v>
+        <v>217116</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>215619</v>
+        <v>215672</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>215602</v>
+        <v>215668</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
@@ -10365,7 +10365,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>214072</v>
+        <v>214112</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
@@ -10403,7 +10403,7 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>212714</v>
+        <v>212821</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
@@ -10441,7 +10441,7 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>212190</v>
+        <v>212203</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>211766</v>
+        <v>211797</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
@@ -10517,7 +10517,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>211678</v>
+        <v>211729</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
@@ -10555,7 +10555,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>211452</v>
+        <v>211480</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
@@ -10593,7 +10593,7 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>211372</v>
+        <v>211415</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>211162</v>
+        <v>211170</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
@@ -10655,35 +10655,35 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>雨与佩特拉</t>
+          <t>去往桃源</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>BV1Jx411C71t</t>
+          <t>BV1dU4y1K7ZC</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>【flower】雨与佩特拉【バルーン】</t>
+          <t>【足立レイ】去往桃源【ピクド】</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>210287</v>
+        <v>210332</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2017-03-09 20:29:19</t>
+          <t>2021-11-19 18:51:53</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>バルーン</t>
+          <t>ピクド</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Vocainfo</t>
+          <t>ゆりがさきなな</t>
         </is>
       </c>
       <c r="H270" t="n">
@@ -10693,35 +10693,35 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Ungray Days</t>
+          <t>雨与佩特拉</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>BV1nK4y1t7ox</t>
+          <t>BV1Jx411C71t</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>【鏡音リン】褪去暗灰之日【ツミキ】</t>
+          <t>【flower】雨与佩特拉【バルーン】</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>210227</v>
+        <v>210310</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2020-05-16 18:13:03</t>
+          <t>2017-03-09 20:29:19</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>ツミキ</t>
+          <t>バルーン</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>羊小星</t>
+          <t>Vocainfo</t>
         </is>
       </c>
       <c r="H271" t="n">
@@ -10745,7 +10745,7 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>210217</v>
+        <v>210255</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
@@ -10769,35 +10769,35 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>去往桃源</t>
+          <t>Ungray Days</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>BV1dU4y1K7ZC</t>
+          <t>BV1nK4y1t7ox</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>【足立レイ】去往桃源【ピクド】</t>
+          <t>【鏡音リン】褪去暗灰之日【ツミキ】</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>210182</v>
+        <v>210247</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2021-11-19 18:51:53</t>
+          <t>2020-05-16 18:13:03</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>ピクド</t>
+          <t>ツミキ</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>ゆりがさきなな</t>
+          <t>羊小星</t>
         </is>
       </c>
       <c r="H273" t="n">
@@ -10821,7 +10821,7 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>209188</v>
+        <v>209207</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>208985</v>
+        <v>209041</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>208872</v>
+        <v>208950</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>208791</v>
+        <v>208815</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>207826</v>
+        <v>207859</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
@@ -11011,7 +11011,7 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>206803</v>
+        <v>206829</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>206579</v>
+        <v>206591</v>
       </c>
       <c r="E280" t="inlineStr">
         <is>
@@ -11087,7 +11087,7 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>206271</v>
+        <v>206289</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>205447</v>
+        <v>205494</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>205377</v>
+        <v>205406</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
@@ -11201,7 +11201,7 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>205141</v>
+        <v>205194</v>
       </c>
       <c r="E284" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>204936</v>
+        <v>204963</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>204693</v>
+        <v>204773</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
@@ -11315,7 +11315,7 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>204533</v>
+        <v>204563</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
@@ -11353,7 +11353,7 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>203462</v>
+        <v>203475</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>203047</v>
+        <v>203063</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>202954</v>
+        <v>202971</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
@@ -11467,7 +11467,7 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>202812</v>
+        <v>202834</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
@@ -11491,35 +11491,35 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Crazy nighT</t>
+          <t>落花</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>BV1gx411F7oJ</t>
+          <t>BV1Ns411B7GG</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>【ボカロ8人】Crazy ∞ nighT【ひとしずくP・やま△】</t>
+          <t>【初音ミク】落花【ナブナ/n-buna】</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>202446</v>
+        <v>202489</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>2012-07-18 18:38:52</t>
+          <t>2016-05-07 18:05:37</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>ひとしずくP・やま△</t>
+          <t>ナブナ</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>BILI君的音樂工房</t>
+          <t>KitanoNani</t>
         </is>
       </c>
       <c r="H292" t="n">
@@ -11529,35 +11529,35 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>落花</t>
+          <t>Crazy nighT</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>BV1Ns411B7GG</t>
+          <t>BV1gx411F7oJ</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>【初音ミク】落花【ナブナ/n-buna】</t>
+          <t>【ボカロ8人】Crazy ∞ nighT【ひとしずくP・やま△】</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>202438</v>
+        <v>202470</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>2016-05-07 18:05:37</t>
+          <t>2012-07-18 18:38:52</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>ナブナ</t>
+          <t>ひとしずくP・やま△</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>KitanoNani</t>
+          <t>BILI君的音樂工房</t>
         </is>
       </c>
       <c r="H293" t="n">
@@ -11581,7 +11581,7 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>202279</v>
+        <v>202418</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>202066</v>
+        <v>202097</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>201498</v>
+        <v>201535</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>201163</v>
+        <v>201183</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
@@ -11719,77 +11719,77 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>浴槽与霓虹灯鱼</t>
+          <t>太糟糕了呐</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>BV193411Y7ZE</t>
+          <t>BV1ZZ42117oR</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>浴槽とネオンテトラ / flower</t>
+          <t>【初音ミク ･ 重音テト ･ ずんだもん】ヤババイナ【さたぱんP】</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>200631</v>
+        <v>200823</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>2022-01-03 22:15:04</t>
+          <t>2024-02-22 19:32:09</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>REISAI</t>
+          <t>さたぱんP</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>REISAI_official</t>
+          <t>青杉折扇</t>
         </is>
       </c>
       <c r="H298" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>太糟糕了呐</t>
+          <t>浴槽与霓虹灯鱼</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>BV1ZZ42117oR</t>
+          <t>BV193411Y7ZE</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>【初音ミク ･ 重音テト ･ ずんだもん】ヤババイナ【さたぱんP】</t>
+          <t>浴槽とネオンテトラ / flower</t>
         </is>
       </c>
       <c r="D299" t="n">
-        <v>200387</v>
+        <v>200684</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>2024-02-22 19:32:09</t>
+          <t>2022-01-03 22:15:04</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>さたぱんP</t>
+          <t>REISAI</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>青杉折扇</t>
+          <t>REISAI_official</t>
         </is>
       </c>
       <c r="H299" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="300">
@@ -11809,7 +11809,7 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>199852</v>
+        <v>200051</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
@@ -11833,68 +11833,68 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Sanzione</t>
+          <t>小兔兔</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>BV1pe41157jE</t>
+          <t>BV1XK4y1s7NF</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>s̔́̕ã̕n͞z͝iơ̐n͑͠e̛̔̃ / 初音ミク  (sanzione / Hatsune Miku)</t>
+          <t>【鳴花ヒメ】小兔兔【youまん】</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>198363</v>
+        <v>198412</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>2022-10-10 16:03:00</t>
+          <t>2020-07-09 17:23:50</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>ざんぎ</t>
+          <t>youまん</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>ざんぎ_Zangi</t>
+          <t>rotbala</t>
         </is>
       </c>
       <c r="H301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>小兔兔</t>
+          <t>狼烟</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>BV1XK4y1s7NF</t>
+          <t>BV1VE411877x</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>【鳴花ヒメ】小兔兔【youまん】</t>
+          <t>【初音ミク】狼煙【john】</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>198327</v>
+        <v>198384</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2020-07-09 17:23:50</t>
+          <t>2019-10-31 20:14:18</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>youまん</t>
+          <t>john</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
@@ -11909,39 +11909,39 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>狼烟</t>
+          <t>Sanzione</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>BV1VE411877x</t>
+          <t>BV1pe41157jE</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>【初音ミク】狼煙【john】</t>
+          <t>s̔́̕ã̕n͞z͝iơ̐n͑͠e̛̔̃ / 初音ミク  (sanzione / Hatsune Miku)</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>198310</v>
+        <v>198383</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2019-10-31 20:14:18</t>
+          <t>2022-10-10 16:03:00</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>john</t>
+          <t>ざんぎ</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>rotbala</t>
+          <t>ざんぎ_Zangi</t>
         </is>
       </c>
       <c r="H303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="304">
@@ -11961,7 +11961,7 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>197712</v>
+        <v>197724</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>197597</v>
+        <v>197623</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>197122</v>
+        <v>197141</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         </is>
       </c>
       <c r="D307" t="n">
-        <v>196555</v>
+        <v>196632</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
@@ -12113,7 +12113,7 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>196146</v>
+        <v>196259</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>195558</v>
+        <v>195576</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>194234</v>
+        <v>194424</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>194165</v>
+        <v>194184</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         </is>
       </c>
       <c r="D312" t="n">
-        <v>193571</v>
+        <v>193698</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         </is>
       </c>
       <c r="D313" t="n">
-        <v>193280</v>
+        <v>193309</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
@@ -12327,77 +12327,77 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>苏州恋慕</t>
+          <t>紫色的向日葵</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>BV1Ns411Q7TL</t>
+          <t>BV1sk4y1G73H</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>【VOCALOID Fukase】蘇州恋慕【みきとP】</t>
+          <t>【羽累】紫色の向日葵/紫色的向日葵【香椎モイミ】</t>
         </is>
       </c>
       <c r="D314" t="n">
-        <v>192688</v>
+        <v>192705</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2016-02-25 18:14:54</t>
+          <t>2023-07-24 10:00:00</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>みきとP</t>
+          <t>香椎モイミ</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>阿赫official</t>
+          <t>香椎モイミ</t>
         </is>
       </c>
       <c r="H314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>紫色的向日葵</t>
+          <t>苏州恋慕</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>BV1sk4y1G73H</t>
+          <t>BV1Ns411Q7TL</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>【羽累】紫色の向日葵/紫色的向日葵【香椎モイミ】</t>
+          <t>【VOCALOID Fukase】蘇州恋慕【みきとP】</t>
         </is>
       </c>
       <c r="D315" t="n">
-        <v>192645</v>
+        <v>192701</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2023-07-24 10:00:00</t>
+          <t>2016-02-25 18:14:54</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>香椎モイミ</t>
+          <t>みきとP</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>香椎モイミ</t>
+          <t>阿赫official</t>
         </is>
       </c>
       <c r="H315" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="316">
@@ -12417,7 +12417,7 @@
         </is>
       </c>
       <c r="D316" t="n">
-        <v>192220</v>
+        <v>192246</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
@@ -12455,7 +12455,7 @@
         </is>
       </c>
       <c r="D317" t="n">
-        <v>191564</v>
+        <v>191594</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         </is>
       </c>
       <c r="D318" t="n">
-        <v>191443</v>
+        <v>191488</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>189882</v>
+        <v>189916</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
         </is>
       </c>
       <c r="D320" t="n">
-        <v>189721</v>
+        <v>189746</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         </is>
       </c>
       <c r="D321" t="n">
-        <v>188749</v>
+        <v>188790</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
         </is>
       </c>
       <c r="D322" t="n">
-        <v>188722</v>
+        <v>188768</v>
       </c>
       <c r="E322" t="inlineStr">
         <is>
@@ -12683,7 +12683,7 @@
         </is>
       </c>
       <c r="D323" t="n">
-        <v>187011</v>
+        <v>187025</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
@@ -12721,7 +12721,7 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>186994</v>
+        <v>187022</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         </is>
       </c>
       <c r="D325" t="n">
-        <v>186243</v>
+        <v>186412</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         </is>
       </c>
       <c r="D326" t="n">
-        <v>186158</v>
+        <v>186177</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         </is>
       </c>
       <c r="D327" t="n">
-        <v>185617</v>
+        <v>185712</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         </is>
       </c>
       <c r="D328" t="n">
-        <v>185451</v>
+        <v>185537</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
@@ -12911,7 +12911,7 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>184215</v>
+        <v>184244</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         </is>
       </c>
       <c r="D330" t="n">
-        <v>184098</v>
+        <v>184161</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         </is>
       </c>
       <c r="D331" t="n">
-        <v>184098</v>
+        <v>184136</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
@@ -13025,7 +13025,7 @@
         </is>
       </c>
       <c r="D332" t="n">
-        <v>184019</v>
+        <v>184031</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
         </is>
       </c>
       <c r="D333" t="n">
-        <v>183755</v>
+        <v>183772</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
@@ -13101,7 +13101,7 @@
         </is>
       </c>
       <c r="D334" t="n">
-        <v>182513</v>
+        <v>182692</v>
       </c>
       <c r="E334" t="inlineStr">
         <is>
@@ -13139,7 +13139,7 @@
         </is>
       </c>
       <c r="D335" t="n">
-        <v>180804</v>
+        <v>180826</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
@@ -13177,7 +13177,7 @@
         </is>
       </c>
       <c r="D336" t="n">
-        <v>180785</v>
+        <v>180802</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         </is>
       </c>
       <c r="D337" t="n">
-        <v>180689</v>
+        <v>180760</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
@@ -13253,7 +13253,7 @@
         </is>
       </c>
       <c r="D338" t="n">
-        <v>180437</v>
+        <v>180460</v>
       </c>
       <c r="E338" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>180130</v>
+        <v>180140</v>
       </c>
       <c r="E339" t="inlineStr">
         <is>
@@ -13329,7 +13329,7 @@
         </is>
       </c>
       <c r="D340" t="n">
-        <v>180046</v>
+        <v>180072</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
@@ -13367,7 +13367,7 @@
         </is>
       </c>
       <c r="D341" t="n">
-        <v>179963</v>
+        <v>179992</v>
       </c>
       <c r="E341" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         </is>
       </c>
       <c r="D342" t="n">
-        <v>179170</v>
+        <v>179256</v>
       </c>
       <c r="E342" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         </is>
       </c>
       <c r="D343" t="n">
-        <v>177853</v>
+        <v>177877</v>
       </c>
       <c r="E343" t="inlineStr">
         <is>
@@ -13481,7 +13481,7 @@
         </is>
       </c>
       <c r="D344" t="n">
-        <v>177717</v>
+        <v>177756</v>
       </c>
       <c r="E344" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>177461</v>
+        <v>177473</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
@@ -13557,7 +13557,7 @@
         </is>
       </c>
       <c r="D346" t="n">
-        <v>177412</v>
+        <v>177429</v>
       </c>
       <c r="E346" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>176488</v>
+        <v>176571</v>
       </c>
       <c r="E347" t="inlineStr">
         <is>
@@ -13633,7 +13633,7 @@
         </is>
       </c>
       <c r="D348" t="n">
-        <v>175950</v>
+        <v>175956</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         </is>
       </c>
       <c r="D349" t="n">
-        <v>175276</v>
+        <v>175314</v>
       </c>
       <c r="E349" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         </is>
       </c>
       <c r="D350" t="n">
-        <v>175153</v>
+        <v>175182</v>
       </c>
       <c r="E350" t="inlineStr">
         <is>
@@ -13747,7 +13747,7 @@
         </is>
       </c>
       <c r="D351" t="n">
-        <v>174678</v>
+        <v>174691</v>
       </c>
       <c r="E351" t="inlineStr">
         <is>
@@ -13785,7 +13785,7 @@
         </is>
       </c>
       <c r="D352" t="n">
-        <v>174604</v>
+        <v>174615</v>
       </c>
       <c r="E352" t="inlineStr">
         <is>
@@ -13809,35 +13809,35 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>消极标签</t>
+          <t>肚子怎么回事？</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>BV1TW411v7Vm</t>
+          <t>BV1gf421d7Ej</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>【flower】消极标签【かいりきベア】</t>
+          <t>【中日字幕/みつあくま】肚子怎么回事？/どーなってんの？ - feat.重音テト</t>
         </is>
       </c>
       <c r="D353" t="n">
-        <v>174000</v>
+        <v>174361</v>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>2018-01-16 20:10:35</t>
+          <t>2024-05-24 21:05:35</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>かいりきベア</t>
+          <t>ラマーズP</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>SenaRinka_Alice</t>
+          <t>かた方</t>
         </is>
       </c>
       <c r="H353" t="n">
@@ -13847,35 +13847,35 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>虽然歌声无形</t>
+          <t>消极标签</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>BV1sx411c7XC</t>
+          <t>BV1TW411v7Vm</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>「歌に形はないけれど」vo.初音ミク</t>
+          <t>【flower】消极标签【かいりきベア】</t>
         </is>
       </c>
       <c r="D354" t="n">
-        <v>173644</v>
+        <v>174020</v>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>2010-02-23 01:35:02</t>
+          <t>2018-01-16 20:10:35</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>doriko</t>
+          <t>かいりきベア</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>ゆっくり</t>
+          <t>SenaRinka_Alice</t>
         </is>
       </c>
       <c r="H354" t="n">
@@ -13885,35 +13885,35 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>肚子怎么回事？</t>
+          <t>虽然歌声无形</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>BV1gf421d7Ej</t>
+          <t>BV1sx411c7XC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>【中日字幕/みつあくま】肚子怎么回事？/どーなってんの？ - feat.重音テト</t>
+          <t>「歌に形はないけれど」vo.初音ミク</t>
         </is>
       </c>
       <c r="D355" t="n">
-        <v>173418</v>
+        <v>173674</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>2024-05-24 21:05:35</t>
+          <t>2010-02-23 01:35:02</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>ラマーズP</t>
+          <t>doriko</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>かた方</t>
+          <t>ゆっくり</t>
         </is>
       </c>
       <c r="H355" t="n">
@@ -13937,7 +13937,7 @@
         </is>
       </c>
       <c r="D356" t="n">
-        <v>173159</v>
+        <v>173176</v>
       </c>
       <c r="E356" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         </is>
       </c>
       <c r="D357" t="n">
-        <v>172666</v>
+        <v>172671</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
@@ -14013,7 +14013,7 @@
         </is>
       </c>
       <c r="D358" t="n">
-        <v>172307</v>
+        <v>172315</v>
       </c>
       <c r="E358" t="inlineStr">
         <is>
@@ -14051,7 +14051,7 @@
         </is>
       </c>
       <c r="D359" t="n">
-        <v>172057</v>
+        <v>172075</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
@@ -14089,7 +14089,7 @@
         </is>
       </c>
       <c r="D360" t="n">
-        <v>171947</v>
+        <v>171972</v>
       </c>
       <c r="E360" t="inlineStr">
         <is>
@@ -14127,7 +14127,7 @@
         </is>
       </c>
       <c r="D361" t="n">
-        <v>171568</v>
+        <v>171582</v>
       </c>
       <c r="E361" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
         </is>
       </c>
       <c r="D362" t="n">
-        <v>171507</v>
+        <v>171550</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
@@ -14189,35 +14189,35 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>为什么酱的主题曲</t>
+          <t>社交恐惧症</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>BV1px411c7xS</t>
+          <t>BV1Ks421G7Kc</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>【初音ミク】 どうしてちゃんのテーマ 【PV】</t>
+          <t>【重音テトSV】社交恐惧症【にほしか】【中文CC字幕】</t>
         </is>
       </c>
       <c r="D363" t="n">
-        <v>171375</v>
+        <v>171477</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>2010-09-25 23:18:03</t>
+          <t>2024-05-24 22:50:47</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>ピノキオピー</t>
+          <t>にほしか</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>精神安定剤</t>
         </is>
       </c>
       <c r="H363" t="n">
@@ -14227,35 +14227,35 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>二息步行</t>
+          <t>为什么酱的主题曲</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>BV1As41187Gw</t>
+          <t>BV1px411c7xS</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>【初音ミク】二息歩行【DECO*27】</t>
+          <t>【初音ミク】 どうしてちゃんのテーマ 【PV】</t>
         </is>
       </c>
       <c r="D364" t="n">
-        <v>171366</v>
+        <v>171402</v>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>2017-01-26 16:33:08</t>
+          <t>2010-09-25 23:18:03</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>DECO*27</t>
+          <t>ピノキオピー</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>羊小星</t>
+          <t>911</t>
         </is>
       </c>
       <c r="H364" t="n">
@@ -14265,35 +14265,35 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>社交恐惧症</t>
+          <t>二息步行</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>BV1Ks421G7Kc</t>
+          <t>BV1As41187Gw</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>【重音テトSV】社交恐惧症【にほしか】【中文CC字幕】</t>
+          <t>【初音ミク】二息歩行【DECO*27】</t>
         </is>
       </c>
       <c r="D365" t="n">
-        <v>171040</v>
+        <v>171395</v>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>2024-05-24 22:50:47</t>
+          <t>2017-01-26 16:33:08</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>にほしか</t>
+          <t>DECO*27</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>精神安定剤</t>
+          <t>羊小星</t>
         </is>
       </c>
       <c r="H365" t="n">
@@ -14317,7 +14317,7 @@
         </is>
       </c>
       <c r="D366" t="n">
-        <v>170888</v>
+        <v>170898</v>
       </c>
       <c r="E366" t="inlineStr">
         <is>
@@ -14355,7 +14355,7 @@
         </is>
       </c>
       <c r="D367" t="n">
-        <v>170690</v>
+        <v>170698</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
         </is>
       </c>
       <c r="D368" t="n">
-        <v>170646</v>
+        <v>170665</v>
       </c>
       <c r="E368" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         </is>
       </c>
       <c r="D369" t="n">
-        <v>170515</v>
+        <v>170646</v>
       </c>
       <c r="E369" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
         </is>
       </c>
       <c r="D370" t="n">
-        <v>170242</v>
+        <v>170267</v>
       </c>
       <c r="E370" t="inlineStr">
         <is>
@@ -14507,7 +14507,7 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>170040</v>
+        <v>170048</v>
       </c>
       <c r="E371" t="inlineStr">
         <is>
@@ -14545,7 +14545,7 @@
         </is>
       </c>
       <c r="D372" t="n">
-        <v>170009</v>
+        <v>170039</v>
       </c>
       <c r="E372" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="D373" t="n">
-        <v>169891</v>
+        <v>169935</v>
       </c>
       <c r="E373" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         </is>
       </c>
       <c r="D374" t="n">
-        <v>169640</v>
+        <v>169654</v>
       </c>
       <c r="E374" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         </is>
       </c>
       <c r="D375" t="n">
-        <v>169189</v>
+        <v>169227</v>
       </c>
       <c r="E375" t="inlineStr">
         <is>
@@ -14697,7 +14697,7 @@
         </is>
       </c>
       <c r="D376" t="n">
-        <v>169164</v>
+        <v>169203</v>
       </c>
       <c r="E376" t="inlineStr">
         <is>
@@ -14735,7 +14735,7 @@
         </is>
       </c>
       <c r="D377" t="n">
-        <v>168666</v>
+        <v>168678</v>
       </c>
       <c r="E377" t="inlineStr">
         <is>
@@ -14773,7 +14773,7 @@
         </is>
       </c>
       <c r="D378" t="n">
-        <v>167995</v>
+        <v>168021</v>
       </c>
       <c r="E378" t="inlineStr">
         <is>
@@ -14811,7 +14811,7 @@
         </is>
       </c>
       <c r="D379" t="n">
-        <v>167351</v>
+        <v>167365</v>
       </c>
       <c r="E379" t="inlineStr">
         <is>
@@ -14849,7 +14849,7 @@
         </is>
       </c>
       <c r="D380" t="n">
-        <v>167260</v>
+        <v>167277</v>
       </c>
       <c r="E380" t="inlineStr">
         <is>
@@ -14887,7 +14887,7 @@
         </is>
       </c>
       <c r="D381" t="n">
-        <v>167143</v>
+        <v>167197</v>
       </c>
       <c r="E381" t="inlineStr">
         <is>
@@ -14911,35 +14911,35 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Question Mark</t>
+          <t>蜜月Un·Deux·Trois</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>BV1Vb411T7C5</t>
+          <t>BV1ux411c7Wg</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>【初音ミク】Question Mark【john】</t>
+          <t>【鏡音リン】蜜月·Un·Deux·Trois【dateken】</t>
         </is>
       </c>
       <c r="D382" t="n">
-        <v>166378</v>
+        <v>166472</v>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>2019-04-14 12:37:24</t>
+          <t>2013-02-15 19:14:39</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>john</t>
+          <t>dateken</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>ンウヱィ窶っィグゑ齧</t>
+          <t>非洲のGUMI酱</t>
         </is>
       </c>
       <c r="H382" t="n">
@@ -14949,35 +14949,35 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>蜜月Un·Deux·Trois</t>
+          <t>Question Mark</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>BV1ux411c7Wg</t>
+          <t>BV1Vb411T7C5</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>【鏡音リン】蜜月·Un·Deux·Trois【dateken】</t>
+          <t>【初音ミク】Question Mark【john】</t>
         </is>
       </c>
       <c r="D383" t="n">
-        <v>166355</v>
+        <v>166402</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>2013-02-15 19:14:39</t>
+          <t>2019-04-14 12:37:24</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>dateken</t>
+          <t>john</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>非洲のGUMI酱</t>
+          <t>ンウヱィ窶っィグゑ齧</t>
         </is>
       </c>
       <c r="H383" t="n">
@@ -15001,7 +15001,7 @@
         </is>
       </c>
       <c r="D384" t="n">
-        <v>166263</v>
+        <v>166341</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         </is>
       </c>
       <c r="D385" t="n">
-        <v>165901</v>
+        <v>165920</v>
       </c>
       <c r="E385" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         </is>
       </c>
       <c r="D386" t="n">
-        <v>165803</v>
+        <v>165871</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         </is>
       </c>
       <c r="D387" t="n">
-        <v>165453</v>
+        <v>165507</v>
       </c>
       <c r="E387" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         </is>
       </c>
       <c r="D388" t="n">
-        <v>165249</v>
+        <v>165264</v>
       </c>
       <c r="E388" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         </is>
       </c>
       <c r="D389" t="n">
-        <v>164830</v>
+        <v>164849</v>
       </c>
       <c r="E389" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         </is>
       </c>
       <c r="D390" t="n">
-        <v>164810</v>
+        <v>164826</v>
       </c>
       <c r="E390" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         </is>
       </c>
       <c r="D391" t="n">
-        <v>164786</v>
+        <v>164802</v>
       </c>
       <c r="E391" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         </is>
       </c>
       <c r="D392" t="n">
-        <v>163919</v>
+        <v>163936</v>
       </c>
       <c r="E392" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         </is>
       </c>
       <c r="D393" t="n">
-        <v>163912</v>
+        <v>163924</v>
       </c>
       <c r="E393" t="inlineStr">
         <is>
@@ -15381,7 +15381,7 @@
         </is>
       </c>
       <c r="D394" t="n">
-        <v>163411</v>
+        <v>163453</v>
       </c>
       <c r="E394" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         </is>
       </c>
       <c r="D395" t="n">
-        <v>162585</v>
+        <v>162592</v>
       </c>
       <c r="E395" t="inlineStr">
         <is>
@@ -15457,7 +15457,7 @@
         </is>
       </c>
       <c r="D396" t="n">
-        <v>161725</v>
+        <v>161930</v>
       </c>
       <c r="E396" t="inlineStr">
         <is>
@@ -15495,7 +15495,7 @@
         </is>
       </c>
       <c r="D397" t="n">
-        <v>161294</v>
+        <v>161314</v>
       </c>
       <c r="E397" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
         </is>
       </c>
       <c r="D398" t="n">
-        <v>159695</v>
+        <v>159710</v>
       </c>
       <c r="E398" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         </is>
       </c>
       <c r="D399" t="n">
-        <v>159346</v>
+        <v>159450</v>
       </c>
       <c r="E399" t="inlineStr">
         <is>
@@ -15609,7 +15609,7 @@
         </is>
       </c>
       <c r="D400" t="n">
-        <v>158444</v>
+        <v>158459</v>
       </c>
       <c r="E400" t="inlineStr">
         <is>
@@ -15647,7 +15647,7 @@
         </is>
       </c>
       <c r="D401" t="n">
-        <v>158053</v>
+        <v>158192</v>
       </c>
       <c r="E401" t="inlineStr">
         <is>
@@ -15685,7 +15685,7 @@
         </is>
       </c>
       <c r="D402" t="n">
-        <v>155821</v>
+        <v>155834</v>
       </c>
       <c r="E402" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         </is>
       </c>
       <c r="D403" t="n">
-        <v>155802</v>
+        <v>155807</v>
       </c>
       <c r="E403" t="inlineStr">
         <is>
@@ -15761,7 +15761,7 @@
         </is>
       </c>
       <c r="D404" t="n">
-        <v>155561</v>
+        <v>155594</v>
       </c>
       <c r="E404" t="inlineStr">
         <is>
@@ -15799,7 +15799,7 @@
         </is>
       </c>
       <c r="D405" t="n">
-        <v>155494</v>
+        <v>155517</v>
       </c>
       <c r="E405" t="inlineStr">
         <is>
@@ -15837,7 +15837,7 @@
         </is>
       </c>
       <c r="D406" t="n">
-        <v>155227</v>
+        <v>155235</v>
       </c>
       <c r="E406" t="inlineStr">
         <is>
@@ -15875,7 +15875,7 @@
         </is>
       </c>
       <c r="D407" t="n">
-        <v>155123</v>
+        <v>155158</v>
       </c>
       <c r="E407" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         </is>
       </c>
       <c r="D408" t="n">
-        <v>154994</v>
+        <v>155092</v>
       </c>
       <c r="E408" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         </is>
       </c>
       <c r="D409" t="n">
-        <v>154517</v>
+        <v>154542</v>
       </c>
       <c r="E409" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         </is>
       </c>
       <c r="D410" t="n">
-        <v>154074</v>
+        <v>154136</v>
       </c>
       <c r="E410" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="D411" t="n">
-        <v>154015</v>
+        <v>154078</v>
       </c>
       <c r="E411" t="inlineStr">
         <is>
@@ -16065,7 +16065,7 @@
         </is>
       </c>
       <c r="D412" t="n">
-        <v>153699</v>
+        <v>153723</v>
       </c>
       <c r="E412" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
         </is>
       </c>
       <c r="D413" t="n">
-        <v>153423</v>
+        <v>153548</v>
       </c>
       <c r="E413" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
         </is>
       </c>
       <c r="D414" t="n">
-        <v>152258</v>
+        <v>152694</v>
       </c>
       <c r="E414" t="inlineStr">
         <is>
@@ -16165,35 +16165,35 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Sweet Devil</t>
+          <t>廉价的属性</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>BV1QJ41137T2</t>
+          <t>BV1cT421v7nL</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>八王子P「Sweet Devil feat.初音ミク」</t>
+          <t>廉价的属性／重音テト（谎言的真实ver）</t>
         </is>
       </c>
       <c r="D415" t="n">
-        <v>152151</v>
+        <v>152501</v>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>2019-09-20 14:26:53</t>
+          <t>2024-06-04 17:07:38</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>八王子P</t>
+          <t>Frog96</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>八王子P_公式</t>
+          <t>Frog96</t>
         </is>
       </c>
       <c r="H415" t="n">
@@ -16203,35 +16203,35 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>原样</t>
+          <t>Sweet Devil</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>BV1QT411E7nQ</t>
+          <t>BV1QJ41137T2</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>【官方投稿】Chinozo「原样 / アリサマ」feat.FloweR</t>
+          <t>八王子P「Sweet Devil feat.初音ミク」</t>
         </is>
       </c>
       <c r="D416" t="n">
-        <v>151608</v>
+        <v>152174</v>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>2022-07-12 18:00:00</t>
+          <t>2019-09-20 14:26:53</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>Chinozo</t>
+          <t>八王子P</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>ChinozoX_X</t>
+          <t>八王子P_公式</t>
         </is>
       </c>
       <c r="H416" t="n">
@@ -16241,35 +16241,35 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>廉价的属性</t>
+          <t>原样</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>BV1cT421v7nL</t>
+          <t>BV1QT411E7nQ</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>廉价的属性／重音テト（谎言的真实ver）</t>
+          <t>【官方投稿】Chinozo「原样 / アリサマ」feat.FloweR</t>
         </is>
       </c>
       <c r="D417" t="n">
-        <v>151270</v>
+        <v>151630</v>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>2024-06-04 17:07:38</t>
+          <t>2022-07-12 18:00:00</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>Frog96</t>
+          <t>Chinozo</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>Frog96</t>
+          <t>ChinozoX_X</t>
         </is>
       </c>
       <c r="H417" t="n">
@@ -16293,7 +16293,7 @@
         </is>
       </c>
       <c r="D418" t="n">
-        <v>150855</v>
+        <v>150961</v>
       </c>
       <c r="E418" t="inlineStr">
         <is>
@@ -16331,7 +16331,7 @@
         </is>
       </c>
       <c r="D419" t="n">
-        <v>150760</v>
+        <v>150774</v>
       </c>
       <c r="E419" t="inlineStr">
         <is>
@@ -16369,7 +16369,7 @@
         </is>
       </c>
       <c r="D420" t="n">
-        <v>150062</v>
+        <v>150076</v>
       </c>
       <c r="E420" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         </is>
       </c>
       <c r="D421" t="n">
-        <v>149817</v>
+        <v>149831</v>
       </c>
       <c r="E421" t="inlineStr">
         <is>
@@ -16445,7 +16445,7 @@
         </is>
       </c>
       <c r="D422" t="n">
-        <v>149586</v>
+        <v>149614</v>
       </c>
       <c r="E422" t="inlineStr">
         <is>
@@ -16483,7 +16483,7 @@
         </is>
       </c>
       <c r="D423" t="n">
-        <v>149473</v>
+        <v>149480</v>
       </c>
       <c r="E423" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         </is>
       </c>
       <c r="D424" t="n">
-        <v>149087</v>
+        <v>149141</v>
       </c>
       <c r="E424" t="inlineStr">
         <is>
@@ -16559,7 +16559,7 @@
         </is>
       </c>
       <c r="D425" t="n">
-        <v>149041</v>
+        <v>149071</v>
       </c>
       <c r="E425" t="inlineStr">
         <is>
@@ -16597,7 +16597,7 @@
         </is>
       </c>
       <c r="D426" t="n">
-        <v>148902</v>
+        <v>148940</v>
       </c>
       <c r="E426" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         </is>
       </c>
       <c r="D427" t="n">
-        <v>147781</v>
+        <v>147814</v>
       </c>
       <c r="E427" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="D428" t="n">
-        <v>147764</v>
+        <v>147789</v>
       </c>
       <c r="E428" t="inlineStr">
         <is>
@@ -16711,7 +16711,7 @@
         </is>
       </c>
       <c r="D429" t="n">
-        <v>147355</v>
+        <v>147402</v>
       </c>
       <c r="E429" t="inlineStr">
         <is>
@@ -16749,7 +16749,7 @@
         </is>
       </c>
       <c r="D430" t="n">
-        <v>146889</v>
+        <v>146911</v>
       </c>
       <c r="E430" t="inlineStr">
         <is>
@@ -16787,7 +16787,7 @@
         </is>
       </c>
       <c r="D431" t="n">
-        <v>146766</v>
+        <v>146797</v>
       </c>
       <c r="E431" t="inlineStr">
         <is>
@@ -16825,7 +16825,7 @@
         </is>
       </c>
       <c r="D432" t="n">
-        <v>146600</v>
+        <v>146620</v>
       </c>
       <c r="E432" t="inlineStr">
         <is>
@@ -16863,7 +16863,7 @@
         </is>
       </c>
       <c r="D433" t="n">
-        <v>146288</v>
+        <v>146300</v>
       </c>
       <c r="E433" t="inlineStr">
         <is>
@@ -16901,7 +16901,7 @@
         </is>
       </c>
       <c r="D434" t="n">
-        <v>146235</v>
+        <v>146255</v>
       </c>
       <c r="E434" t="inlineStr">
         <is>
@@ -16939,7 +16939,7 @@
         </is>
       </c>
       <c r="D435" t="n">
-        <v>145959</v>
+        <v>145984</v>
       </c>
       <c r="E435" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         </is>
       </c>
       <c r="D436" t="n">
-        <v>145552</v>
+        <v>145578</v>
       </c>
       <c r="E436" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         </is>
       </c>
       <c r="D437" t="n">
-        <v>144852</v>
+        <v>144877</v>
       </c>
       <c r="E437" t="inlineStr">
         <is>
@@ -17053,7 +17053,7 @@
         </is>
       </c>
       <c r="D438" t="n">
-        <v>144669</v>
+        <v>144693</v>
       </c>
       <c r="E438" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         </is>
       </c>
       <c r="D439" t="n">
-        <v>143771</v>
+        <v>143795</v>
       </c>
       <c r="E439" t="inlineStr">
         <is>
@@ -17129,7 +17129,7 @@
         </is>
       </c>
       <c r="D440" t="n">
-        <v>143688</v>
+        <v>143702</v>
       </c>
       <c r="E440" t="inlineStr">
         <is>
@@ -17167,7 +17167,7 @@
         </is>
       </c>
       <c r="D441" t="n">
-        <v>142769</v>
+        <v>142777</v>
       </c>
       <c r="E441" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         </is>
       </c>
       <c r="D442" t="n">
-        <v>142404</v>
+        <v>142485</v>
       </c>
       <c r="E442" t="inlineStr">
         <is>
@@ -17243,7 +17243,7 @@
         </is>
       </c>
       <c r="D443" t="n">
-        <v>142342</v>
+        <v>142359</v>
       </c>
       <c r="E443" t="inlineStr">
         <is>
@@ -17281,7 +17281,7 @@
         </is>
       </c>
       <c r="D444" t="n">
-        <v>142027</v>
+        <v>142069</v>
       </c>
       <c r="E444" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         </is>
       </c>
       <c r="D445" t="n">
-        <v>141871</v>
+        <v>141878</v>
       </c>
       <c r="E445" t="inlineStr">
         <is>
@@ -17343,35 +17343,35 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>你的百科</t>
+          <t>大失败!</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>BV1SW411t71Z</t>
+          <t>BV1sM4m1z7SN</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>【鏡音リン・レン】你的百科【Junky】</t>
+          <t>【重音テトSV/中字】大失败!/Fumble!/ふぁんぶる!（藤原ハガネ）</t>
         </is>
       </c>
       <c r="D446" t="n">
-        <v>140998</v>
+        <v>141531</v>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>2017-12-27 19:33:29</t>
+          <t>2024-06-03 12:00:00</t>
         </is>
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>Junky</t>
+          <t>藤原ハガネ</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>阿赫official</t>
+          <t>苏维埃冰棺中的伊利亚</t>
         </is>
       </c>
       <c r="H446" t="n">
@@ -17381,30 +17381,30 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>PARTY ROCK ETERNITY</t>
+          <t>你的百科</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>BV17x421f7k6</t>
+          <t>BV1SW411t71Z</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>【宝可梦 × 初音未来联动曲第十四首】【中文CC字幕】PARTY ROCK ETERNITY feat. 初音ミク【八王子P】</t>
+          <t>【鏡音リン・レン】你的百科【Junky】</t>
         </is>
       </c>
       <c r="D447" t="n">
-        <v>140670</v>
+        <v>141008</v>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>2024-02-23 17:41:17</t>
+          <t>2017-12-27 19:33:29</t>
         </is>
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>八王子P</t>
+          <t>Junky</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
@@ -17419,35 +17419,35 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Nightmare(Azari)</t>
+          <t>PARTY ROCK ETERNITY</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>BV1uf4y1F7fb</t>
+          <t>BV17x421f7k6</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>【flower】Nightmare【Azari】</t>
+          <t>【宝可梦 × 初音未来联动曲第十四首】【中文CC字幕】PARTY ROCK ETERNITY feat. 初音ミク【八王子P】</t>
         </is>
       </c>
       <c r="D448" t="n">
-        <v>140452</v>
+        <v>140741</v>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>2022-01-21 17:14:47</t>
+          <t>2024-02-23 17:41:17</t>
         </is>
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>Azari</t>
+          <t>八王子P</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>rotbala</t>
+          <t>阿赫official</t>
         </is>
       </c>
       <c r="H448" t="n">
@@ -17457,35 +17457,35 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>大失败!</t>
+          <t>Nightmare(Azari)</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>BV1sM4m1z7SN</t>
+          <t>BV1uf4y1F7fb</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>【重音テトSV/中字】大失败!/Fumble!/ふぁんぶる!（藤原ハガネ）</t>
+          <t>【flower】Nightmare【Azari】</t>
         </is>
       </c>
       <c r="D449" t="n">
-        <v>140431</v>
+        <v>140483</v>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>2024-06-03 12:00:00</t>
+          <t>2022-01-21 17:14:47</t>
         </is>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>藤原ハガネ</t>
+          <t>Azari</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>苏维埃冰棺中的伊利亚</t>
+          <t>rotbala</t>
         </is>
       </c>
       <c r="H449" t="n">
@@ -17509,7 +17509,7 @@
         </is>
       </c>
       <c r="D450" t="n">
-        <v>139266</v>
+        <v>139283</v>
       </c>
       <c r="E450" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         </is>
       </c>
       <c r="D451" t="n">
-        <v>139200</v>
+        <v>139221</v>
       </c>
       <c r="E451" t="inlineStr">
         <is>
@@ -17585,7 +17585,7 @@
         </is>
       </c>
       <c r="D452" t="n">
-        <v>139062</v>
+        <v>139075</v>
       </c>
       <c r="E452" t="inlineStr">
         <is>
@@ -17623,7 +17623,7 @@
         </is>
       </c>
       <c r="D453" t="n">
-        <v>138842</v>
+        <v>138865</v>
       </c>
       <c r="E453" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         </is>
       </c>
       <c r="D454" t="n">
-        <v>138615</v>
+        <v>138673</v>
       </c>
       <c r="E454" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         </is>
       </c>
       <c r="D455" t="n">
-        <v>137186</v>
+        <v>137234</v>
       </c>
       <c r="E455" t="inlineStr">
         <is>
@@ -17737,7 +17737,7 @@
         </is>
       </c>
       <c r="D456" t="n">
-        <v>137105</v>
+        <v>137126</v>
       </c>
       <c r="E456" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         </is>
       </c>
       <c r="D457" t="n">
-        <v>136869</v>
+        <v>137107</v>
       </c>
       <c r="E457" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         </is>
       </c>
       <c r="D458" t="n">
-        <v>136799</v>
+        <v>136812</v>
       </c>
       <c r="E458" t="inlineStr">
         <is>
@@ -17851,7 +17851,7 @@
         </is>
       </c>
       <c r="D459" t="n">
-        <v>136407</v>
+        <v>136433</v>
       </c>
       <c r="E459" t="inlineStr">
         <is>
@@ -17889,7 +17889,7 @@
         </is>
       </c>
       <c r="D460" t="n">
-        <v>136303</v>
+        <v>136323</v>
       </c>
       <c r="E460" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         </is>
       </c>
       <c r="D461" t="n">
-        <v>136202</v>
+        <v>136213</v>
       </c>
       <c r="E461" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         </is>
       </c>
       <c r="D462" t="n">
-        <v>135747</v>
+        <v>135764</v>
       </c>
       <c r="E462" t="inlineStr">
         <is>
@@ -18003,7 +18003,7 @@
         </is>
       </c>
       <c r="D463" t="n">
-        <v>135506</v>
+        <v>135538</v>
       </c>
       <c r="E463" t="inlineStr">
         <is>
@@ -18041,7 +18041,7 @@
         </is>
       </c>
       <c r="D464" t="n">
-        <v>135311</v>
+        <v>135330</v>
       </c>
       <c r="E464" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
         </is>
       </c>
       <c r="D465" t="n">
-        <v>135066</v>
+        <v>135089</v>
       </c>
       <c r="E465" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         </is>
       </c>
       <c r="D466" t="n">
-        <v>134796</v>
+        <v>134805</v>
       </c>
       <c r="E466" t="inlineStr">
         <is>
@@ -18155,7 +18155,7 @@
         </is>
       </c>
       <c r="D467" t="n">
-        <v>134595</v>
+        <v>134611</v>
       </c>
       <c r="E467" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         </is>
       </c>
       <c r="D468" t="n">
-        <v>134096</v>
+        <v>134111</v>
       </c>
       <c r="E468" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
         </is>
       </c>
       <c r="D469" t="n">
-        <v>133934</v>
+        <v>133948</v>
       </c>
       <c r="E469" t="inlineStr">
         <is>
@@ -18269,7 +18269,7 @@
         </is>
       </c>
       <c r="D470" t="n">
-        <v>133639</v>
+        <v>133658</v>
       </c>
       <c r="E470" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         </is>
       </c>
       <c r="D471" t="n">
-        <v>133254</v>
+        <v>133272</v>
       </c>
       <c r="E471" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         </is>
       </c>
       <c r="D472" t="n">
-        <v>133178</v>
+        <v>133197</v>
       </c>
       <c r="E472" t="inlineStr">
         <is>
@@ -18369,77 +18369,77 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>超真人实境秀</t>
+          <t>啊啊，美妙的喵生</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>BV1hb411g7Qb</t>
+          <t>BV1fx411c79K</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>【初音未来】超真人實境秀 / Hyper Reality Show【Utsu-P/鬱P】</t>
+          <t>【GUMI×鏡音レン】嗚呼、素晴らしきニャン生</t>
         </is>
       </c>
       <c r="D473" t="n">
-        <v>132998</v>
+        <v>133126</v>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>2019-04-05 12:31:19</t>
+          <t>2011-07-11 19:49:28</t>
         </is>
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>Utsu-P</t>
+          <t>Nem</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>Utsu-P</t>
+          <t>死ぬほど愛されて眠れない</t>
         </is>
       </c>
       <c r="H473" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>啊啊，美妙的喵生</t>
+          <t>超真人实境秀</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>BV1fx411c79K</t>
+          <t>BV1hb411g7Qb</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>【GUMI×鏡音レン】嗚呼、素晴らしきニャン生</t>
+          <t>【初音未来】超真人實境秀 / Hyper Reality Show【Utsu-P/鬱P】</t>
         </is>
       </c>
       <c r="D474" t="n">
-        <v>132988</v>
+        <v>133014</v>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>2011-07-11 19:49:28</t>
+          <t>2019-04-05 12:31:19</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>Nem</t>
+          <t>Utsu-P</t>
         </is>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>死ぬほど愛されて眠れない</t>
+          <t>Utsu-P</t>
         </is>
       </c>
       <c r="H474" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="475">
@@ -18459,7 +18459,7 @@
         </is>
       </c>
       <c r="D475" t="n">
-        <v>132701</v>
+        <v>132718</v>
       </c>
       <c r="E475" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         </is>
       </c>
       <c r="D476" t="n">
-        <v>131700</v>
+        <v>131733</v>
       </c>
       <c r="E476" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         </is>
       </c>
       <c r="D477" t="n">
-        <v>131210</v>
+        <v>131258</v>
       </c>
       <c r="E477" t="inlineStr">
         <is>
@@ -18573,7 +18573,7 @@
         </is>
       </c>
       <c r="D478" t="n">
-        <v>131086</v>
+        <v>131122</v>
       </c>
       <c r="E478" t="inlineStr">
         <is>
@@ -18611,7 +18611,7 @@
         </is>
       </c>
       <c r="D479" t="n">
-        <v>128322</v>
+        <v>128329</v>
       </c>
       <c r="E479" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         </is>
       </c>
       <c r="D480" t="n">
-        <v>128217</v>
+        <v>128230</v>
       </c>
       <c r="E480" t="inlineStr">
         <is>
@@ -18687,7 +18687,7 @@
         </is>
       </c>
       <c r="D481" t="n">
-        <v>127932</v>
+        <v>127960</v>
       </c>
       <c r="E481" t="inlineStr">
         <is>
@@ -18725,7 +18725,7 @@
         </is>
       </c>
       <c r="D482" t="n">
-        <v>127724</v>
+        <v>127745</v>
       </c>
       <c r="E482" t="inlineStr">
         <is>
@@ -18763,7 +18763,7 @@
         </is>
       </c>
       <c r="D483" t="n">
-        <v>127622</v>
+        <v>127634</v>
       </c>
       <c r="E483" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         </is>
       </c>
       <c r="D484" t="n">
-        <v>127271</v>
+        <v>127292</v>
       </c>
       <c r="E484" t="inlineStr">
         <is>
@@ -18839,7 +18839,7 @@
         </is>
       </c>
       <c r="D485" t="n">
-        <v>126734</v>
+        <v>126744</v>
       </c>
       <c r="E485" t="inlineStr">
         <is>
@@ -18877,7 +18877,7 @@
         </is>
       </c>
       <c r="D486" t="n">
-        <v>126711</v>
+        <v>126726</v>
       </c>
       <c r="E486" t="inlineStr">
         <is>
@@ -18915,7 +18915,7 @@
         </is>
       </c>
       <c r="D487" t="n">
-        <v>126545</v>
+        <v>126654</v>
       </c>
       <c r="E487" t="inlineStr">
         <is>
@@ -18953,7 +18953,7 @@
         </is>
       </c>
       <c r="D488" t="n">
-        <v>125448</v>
+        <v>125486</v>
       </c>
       <c r="E488" t="inlineStr">
         <is>
@@ -18991,7 +18991,7 @@
         </is>
       </c>
       <c r="D489" t="n">
-        <v>125259</v>
+        <v>125283</v>
       </c>
       <c r="E489" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         </is>
       </c>
       <c r="D490" t="n">
-        <v>124748</v>
+        <v>124776</v>
       </c>
       <c r="E490" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         </is>
       </c>
       <c r="D491" t="n">
-        <v>124676</v>
+        <v>124687</v>
       </c>
       <c r="E491" t="inlineStr">
         <is>
@@ -19105,7 +19105,7 @@
         </is>
       </c>
       <c r="D492" t="n">
-        <v>124206</v>
+        <v>124220</v>
       </c>
       <c r="E492" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         </is>
       </c>
       <c r="D493" t="n">
-        <v>123754</v>
+        <v>123761</v>
       </c>
       <c r="E493" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         </is>
       </c>
       <c r="D494" t="n">
-        <v>123198</v>
+        <v>123209</v>
       </c>
       <c r="E494" t="inlineStr">
         <is>
@@ -19219,7 +19219,7 @@
         </is>
       </c>
       <c r="D495" t="n">
-        <v>122501</v>
+        <v>122508</v>
       </c>
       <c r="E495" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         </is>
       </c>
       <c r="D496" t="n">
-        <v>121753</v>
+        <v>121777</v>
       </c>
       <c r="E496" t="inlineStr">
         <is>
@@ -19295,7 +19295,7 @@
         </is>
       </c>
       <c r="D497" t="n">
-        <v>121594</v>
+        <v>121606</v>
       </c>
       <c r="E497" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         </is>
       </c>
       <c r="D498" t="n">
-        <v>121069</v>
+        <v>121106</v>
       </c>
       <c r="E498" t="inlineStr">
         <is>
@@ -19371,7 +19371,7 @@
         </is>
       </c>
       <c r="D499" t="n">
-        <v>120130</v>
+        <v>120139</v>
       </c>
       <c r="E499" t="inlineStr">
         <is>
@@ -19409,7 +19409,7 @@
         </is>
       </c>
       <c r="D500" t="n">
-        <v>120112</v>
+        <v>120132</v>
       </c>
       <c r="E500" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         </is>
       </c>
       <c r="D501" t="n">
-        <v>120034</v>
+        <v>120045</v>
       </c>
       <c r="E501" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         </is>
       </c>
       <c r="D502" t="n">
-        <v>119993</v>
+        <v>120040</v>
       </c>
       <c r="E502" t="inlineStr">
         <is>
@@ -19523,7 +19523,7 @@
         </is>
       </c>
       <c r="D503" t="n">
-        <v>119318</v>
+        <v>119361</v>
       </c>
       <c r="E503" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         </is>
       </c>
       <c r="D504" t="n">
-        <v>119069</v>
+        <v>119084</v>
       </c>
       <c r="E504" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         </is>
       </c>
       <c r="D505" t="n">
-        <v>118941</v>
+        <v>119026</v>
       </c>
       <c r="E505" t="inlineStr">
         <is>
@@ -19637,7 +19637,7 @@
         </is>
       </c>
       <c r="D506" t="n">
-        <v>118938</v>
+        <v>118952</v>
       </c>
       <c r="E506" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         </is>
       </c>
       <c r="D507" t="n">
-        <v>118872</v>
+        <v>118914</v>
       </c>
       <c r="E507" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         </is>
       </c>
       <c r="D508" t="n">
-        <v>118661</v>
+        <v>118729</v>
       </c>
       <c r="E508" t="inlineStr">
         <is>
@@ -19751,7 +19751,7 @@
         </is>
       </c>
       <c r="D509" t="n">
-        <v>118473</v>
+        <v>118500</v>
       </c>
       <c r="E509" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         </is>
       </c>
       <c r="D510" t="n">
-        <v>117398</v>
+        <v>117408</v>
       </c>
       <c r="E510" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         </is>
       </c>
       <c r="D511" t="n">
-        <v>117098</v>
+        <v>117112</v>
       </c>
       <c r="E511" t="inlineStr">
         <is>
@@ -19865,7 +19865,7 @@
         </is>
       </c>
       <c r="D512" t="n">
-        <v>116641</v>
+        <v>116660</v>
       </c>
       <c r="E512" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         </is>
       </c>
       <c r="D513" t="n">
-        <v>116428</v>
+        <v>116455</v>
       </c>
       <c r="E513" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         </is>
       </c>
       <c r="D514" t="n">
-        <v>115846</v>
+        <v>115860</v>
       </c>
       <c r="E514" t="inlineStr">
         <is>
@@ -19979,7 +19979,7 @@
         </is>
       </c>
       <c r="D515" t="n">
-        <v>115743</v>
+        <v>115771</v>
       </c>
       <c r="E515" t="inlineStr">
         <is>
@@ -20003,77 +20003,77 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>EAZY DANCE</t>
+          <t>此空都满满装填</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>BV1Lx411w7w8</t>
+          <t>BV14h4y1G7Mi</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>【初音ミク人间调教】イージーデンス【Mitchie M】</t>
+          <t>空を満たして／可不（Fill Me / KAFU）</t>
         </is>
       </c>
       <c r="D516" t="n">
-        <v>115444</v>
+        <v>115460</v>
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>2012-01-02 14:12:40</t>
+          <t>2023-06-08 07:46:58</t>
         </is>
       </c>
       <c r="F516" t="inlineStr">
         <is>
-          <t>MitchieM</t>
+          <t>Frog96</t>
         </is>
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>【存在抹消】</t>
+          <t>Frog96</t>
         </is>
       </c>
       <c r="H516" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>此空都满满装填</t>
+          <t>EAZY DANCE</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>BV14h4y1G7Mi</t>
+          <t>BV1Lx411w7w8</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>空を満たして／可不（Fill Me / KAFU）</t>
+          <t>【初音ミク人间调教】イージーデンス【Mitchie M】</t>
         </is>
       </c>
       <c r="D517" t="n">
-        <v>115390</v>
+        <v>115452</v>
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>2023-06-08 07:46:58</t>
+          <t>2012-01-02 14:12:40</t>
         </is>
       </c>
       <c r="F517" t="inlineStr">
         <is>
-          <t>Frog96</t>
+          <t>MitchieM</t>
         </is>
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>Frog96</t>
+          <t>【存在抹消】</t>
         </is>
       </c>
       <c r="H517" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="518">
@@ -20093,7 +20093,7 @@
         </is>
       </c>
       <c r="D518" t="n">
-        <v>115096</v>
+        <v>115144</v>
       </c>
       <c r="E518" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         </is>
       </c>
       <c r="D519" t="n">
-        <v>114795</v>
+        <v>114811</v>
       </c>
       <c r="E519" t="inlineStr">
         <is>
@@ -20169,7 +20169,7 @@
         </is>
       </c>
       <c r="D520" t="n">
-        <v>114587</v>
+        <v>114625</v>
       </c>
       <c r="E520" t="inlineStr">
         <is>
@@ -20207,7 +20207,7 @@
         </is>
       </c>
       <c r="D521" t="n">
-        <v>114564</v>
+        <v>114585</v>
       </c>
       <c r="E521" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         </is>
       </c>
       <c r="D522" t="n">
-        <v>114160</v>
+        <v>114175</v>
       </c>
       <c r="E522" t="inlineStr">
         <is>
@@ -20283,7 +20283,7 @@
         </is>
       </c>
       <c r="D523" t="n">
-        <v>114131</v>
+        <v>114155</v>
       </c>
       <c r="E523" t="inlineStr">
         <is>
@@ -20321,7 +20321,7 @@
         </is>
       </c>
       <c r="D524" t="n">
-        <v>113533</v>
+        <v>113570</v>
       </c>
       <c r="E524" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         </is>
       </c>
       <c r="D525" t="n">
-        <v>113397</v>
+        <v>113422</v>
       </c>
       <c r="E525" t="inlineStr">
         <is>
@@ -20397,7 +20397,7 @@
         </is>
       </c>
       <c r="D526" t="n">
-        <v>112882</v>
+        <v>112929</v>
       </c>
       <c r="E526" t="inlineStr">
         <is>
@@ -20435,7 +20435,7 @@
         </is>
       </c>
       <c r="D527" t="n">
-        <v>112555</v>
+        <v>112593</v>
       </c>
       <c r="E527" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         </is>
       </c>
       <c r="D528" t="n">
-        <v>112392</v>
+        <v>112456</v>
       </c>
       <c r="E528" t="inlineStr">
         <is>
@@ -20511,7 +20511,7 @@
         </is>
       </c>
       <c r="D529" t="n">
-        <v>112192</v>
+        <v>112211</v>
       </c>
       <c r="E529" t="inlineStr">
         <is>
@@ -20535,77 +20535,77 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>与你一同翱翔天际</t>
+          <t>Positive Dance Time</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>BV1hC4y1R73r</t>
+          <t>BV1vW411h7fX</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>【宝可梦 × 初音未来联动曲第六首】【中文CC字幕】【初音ミク &amp; 巡音ルカ】きみとそらをとぶ（与你翱游天际）【傘村トータ】</t>
+          <t>ポジティブ☆ダンスタイム／キノシタ(kinoshita) feat.音街ウナ・鏡音リン／Positive☆Dance Time</t>
         </is>
       </c>
       <c r="D530" t="n">
-        <v>112152</v>
+        <v>112177</v>
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>2023-12-08 17:45:18</t>
+          <t>2017-12-10 20:49:15</t>
         </is>
       </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t>傘村トータ</t>
+          <t>キノシタ</t>
         </is>
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>阿赫official</t>
+          <t>k1n0shita</t>
         </is>
       </c>
       <c r="H530" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>Positive Dance Time</t>
+          <t>与你一同翱翔天际</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>BV1vW411h7fX</t>
+          <t>BV1hC4y1R73r</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>ポジティブ☆ダンスタイム／キノシタ(kinoshita) feat.音街ウナ・鏡音リン／Positive☆Dance Time</t>
+          <t>【宝可梦 × 初音未来联动曲第六首】【中文CC字幕】【初音ミク &amp; 巡音ルカ】きみとそらをとぶ（与你翱游天际）【傘村トータ】</t>
         </is>
       </c>
       <c r="D531" t="n">
-        <v>112137</v>
+        <v>112176</v>
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>2017-12-10 20:49:15</t>
+          <t>2023-12-08 17:45:18</t>
         </is>
       </c>
       <c r="F531" t="inlineStr">
         <is>
-          <t>キノシタ</t>
+          <t>傘村トータ</t>
         </is>
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>k1n0shita</t>
+          <t>阿赫official</t>
         </is>
       </c>
       <c r="H531" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="532">
@@ -20625,7 +20625,7 @@
         </is>
       </c>
       <c r="D532" t="n">
-        <v>111917</v>
+        <v>111990</v>
       </c>
       <c r="E532" t="inlineStr">
         <is>
@@ -20663,7 +20663,7 @@
         </is>
       </c>
       <c r="D533" t="n">
-        <v>111772</v>
+        <v>111790</v>
       </c>
       <c r="E533" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         </is>
       </c>
       <c r="D534" t="n">
-        <v>111506</v>
+        <v>111538</v>
       </c>
       <c r="E534" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         </is>
       </c>
       <c r="D535" t="n">
-        <v>110912</v>
+        <v>110923</v>
       </c>
       <c r="E535" t="inlineStr">
         <is>
@@ -20777,7 +20777,7 @@
         </is>
       </c>
       <c r="D536" t="n">
-        <v>110664</v>
+        <v>110672</v>
       </c>
       <c r="E536" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         </is>
       </c>
       <c r="D537" t="n">
-        <v>110262</v>
+        <v>110269</v>
       </c>
       <c r="E537" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         </is>
       </c>
       <c r="D538" t="n">
-        <v>109991</v>
+        <v>110011</v>
       </c>
       <c r="E538" t="inlineStr">
         <is>
@@ -20891,7 +20891,7 @@
         </is>
       </c>
       <c r="D539" t="n">
-        <v>58081</v>
+        <v>58524</v>
       </c>
       <c r="E539" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         </is>
       </c>
       <c r="D540" t="n">
-        <v>41937</v>
+        <v>42277</v>
       </c>
       <c r="E540" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         </is>
       </c>
       <c r="D541" t="n">
-        <v>40348</v>
+        <v>41043</v>
       </c>
       <c r="E541" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         </is>
       </c>
       <c r="D542" t="n">
-        <v>35605</v>
+        <v>35771</v>
       </c>
       <c r="E542" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         </is>
       </c>
       <c r="D543" t="n">
-        <v>30443</v>
+        <v>31083</v>
       </c>
       <c r="E543" t="inlineStr">
         <is>
@@ -21081,7 +21081,7 @@
         </is>
       </c>
       <c r="D544" t="n">
-        <v>28864</v>
+        <v>30005</v>
       </c>
       <c r="E544" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         </is>
       </c>
       <c r="D545" t="n">
-        <v>25827</v>
+        <v>27053</v>
       </c>
       <c r="E545" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         </is>
       </c>
       <c r="D546" t="n">
-        <v>23263</v>
+        <v>24640</v>
       </c>
       <c r="E546" t="inlineStr">
         <is>
@@ -21195,7 +21195,7 @@
         </is>
       </c>
       <c r="D547" t="n">
-        <v>22301</v>
+        <v>24467</v>
       </c>
       <c r="E547" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         </is>
       </c>
       <c r="D548" t="n">
-        <v>13142</v>
+        <v>15570</v>
       </c>
       <c r="E548" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         </is>
       </c>
       <c r="D549" t="n">
-        <v>12823</v>
+        <v>14533</v>
       </c>
       <c r="E549" t="inlineStr">
         <is>
@@ -21309,7 +21309,7 @@
         </is>
       </c>
       <c r="D550" t="n">
-        <v>9747</v>
+        <v>10360</v>
       </c>
       <c r="E550" t="inlineStr">
         <is>
@@ -21347,7 +21347,7 @@
         </is>
       </c>
       <c r="D551" t="n">
-        <v>5345</v>
+        <v>5803</v>
       </c>
       <c r="E551" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         </is>
       </c>
       <c r="D552" t="n">
-        <v>4662</v>
+        <v>5114</v>
       </c>
       <c r="E552" t="inlineStr">
         <is>
@@ -21423,7 +21423,7 @@
         </is>
       </c>
       <c r="D553" t="n">
-        <v>4508</v>
+        <v>5021</v>
       </c>
       <c r="E553" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         </is>
       </c>
       <c r="D554" t="n">
-        <v>4119</v>
+        <v>4305</v>
       </c>
       <c r="E554" t="inlineStr">
         <is>
@@ -21485,31 +21485,35 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>把大家都tetoteto掉!!!</t>
+          <t>phony(花p)</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>BV17r421F7MJ</t>
+          <t>BV1Vm42157vT</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>【重音SV】把大家都tetoteto掉！！！ 文艺复兴</t>
+          <t>（remix）变成了早期积木感觉的伪物【Full.ver】</t>
         </is>
       </c>
       <c r="D555" t="n">
-        <v>3321</v>
+        <v>3536</v>
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>2024-06-27 12:30:32</t>
-        </is>
-      </c>
-      <c r="F555" t="inlineStr"/>
+          <t>2024-06-29 12:00:00</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>花p</t>
+        </is>
+      </c>
       <c r="G555" t="inlineStr">
         <is>
-          <t>七草L</t>
+          <t>花p_はなピ</t>
         </is>
       </c>
       <c r="H555" t="n">
@@ -21519,35 +21523,31 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>phony(花p)</t>
+          <t>把大家都tetoteto掉!!!</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>BV1Vm42157vT</t>
+          <t>BV17r421F7MJ</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>（remix）变成了早期积木感觉的伪物【Full.ver】</t>
+          <t>【重音SV】把大家都tetoteto掉！！！ 文艺复兴</t>
         </is>
       </c>
       <c r="D556" t="n">
-        <v>3317</v>
+        <v>3353</v>
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>2024-06-29 12:00:00</t>
-        </is>
-      </c>
-      <c r="F556" t="inlineStr">
-        <is>
-          <t>花p</t>
-        </is>
-      </c>
+          <t>2024-06-27 12:30:32</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr"/>
       <c r="G556" t="inlineStr">
         <is>
-          <t>花p_はなピ</t>
+          <t>七草L</t>
         </is>
       </c>
       <c r="H556" t="n">
@@ -21571,7 +21571,7 @@
         </is>
       </c>
       <c r="D557" t="n">
-        <v>2604</v>
+        <v>2779</v>
       </c>
       <c r="E557" t="inlineStr">
         <is>
@@ -21595,35 +21595,35 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>变成猫不就好了吗！？</t>
+          <t>从相合伞漏出的肢体</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>BV1yn4y1X7m5</t>
+          <t>BV1t4421S7w5</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>【鏡音リン・レン】ネコになっちゃえばいーじゃん！？【OZON】</t>
+          <t>【重音テト】从相合伞漏出的肢体【式浦躁吾】</t>
         </is>
       </c>
       <c r="D558" t="n">
-        <v>790</v>
+        <v>2258</v>
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>2024-06-29 18:16:19</t>
+          <t>2024-06-29 20:12:18</t>
         </is>
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>OZON</t>
+          <t>式浦躁吾</t>
         </is>
       </c>
       <c r="G558" t="inlineStr">
         <is>
-          <t>kttts</t>
+          <t>精神安定剤</t>
         </is>
       </c>
       <c r="H558" t="n">
@@ -21633,35 +21633,35 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>弥留之际(茨)</t>
+          <t>存活千年(染冉)</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>BV1FuhMeZEDs</t>
+          <t>BV1LM4m1m7yf</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>【初投稿/vflower】今わの際に（弥留之际）/茨</t>
+          <t>【重音Neki】存活千年（1000年生きてる）</t>
         </is>
       </c>
       <c r="D559" t="n">
-        <v>462</v>
+        <v>2196</v>
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>2024-06-29 22:35:38</t>
+          <t>2024-06-29 20:07:00</t>
         </is>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>茨</t>
+          <t>染冉</t>
         </is>
       </c>
       <c r="G559" t="inlineStr">
         <is>
-          <t>夏野の茨</t>
+          <t>反复无常卢克</t>
         </is>
       </c>
       <c r="H559" t="n">
@@ -21671,111 +21671,111 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>从相合伞漏出的肢体</t>
+          <t>我想要随风摇摆</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>BV1t4421S7w5</t>
+          <t>BV1Zm421373j</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>【重音テト】从相合伞漏出的肢体【式浦躁吾】</t>
+          <t>【wanna waver】揺らいでいたい feat. 初音ミク ／ でんちゃそ</t>
         </is>
       </c>
       <c r="D560" t="n">
-        <v>492</v>
+        <v>2002</v>
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>2024-06-29 20:12:18</t>
+          <t>2024-06-28 18:00:00</t>
         </is>
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t>式浦躁吾</t>
+          <t>でんちゃそ</t>
         </is>
       </c>
       <c r="G560" t="inlineStr">
         <is>
-          <t>精神安定剤</t>
+          <t>でんちゃそ</t>
         </is>
       </c>
       <c r="H560" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>存活千年(染冉)</t>
+          <t>变成猫不就好了吗！？</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>BV1LM4m1m7yf</t>
+          <t>BV1yn4y1X7m5</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>【重音Neki】存活千年（1000年生きてる）</t>
+          <t>【鏡音リン・レン】ネコになっちゃえばいーじゃん！？【OZON】</t>
         </is>
       </c>
       <c r="D561" t="n">
-        <v>877</v>
+        <v>1145</v>
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>2024-06-29 20:07:00</t>
+          <t>2024-06-29 18:16:19</t>
         </is>
       </c>
       <c r="F561" t="inlineStr">
         <is>
-          <t>染冉</t>
+          <t>OZON</t>
         </is>
       </c>
       <c r="G561" t="inlineStr">
         <is>
-          <t>反复无常卢克</t>
+          <t>kttts</t>
         </is>
       </c>
       <c r="H561" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>我想要随风摇摆</t>
+          <t>弥留之际(茨)</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>BV1Zm421373j</t>
+          <t>BV1FuhMeZEDs</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>【wanna waver】揺らいでいたい feat. 初音ミク ／ でんちゃそ</t>
+          <t>【初投稿/vflower】今わの際に（弥留之际）/茨</t>
         </is>
       </c>
       <c r="D562" t="n">
-        <v>223</v>
+        <v>1051</v>
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>2024-06-28 18:00:00</t>
+          <t>2024-06-29 22:35:38</t>
         </is>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>でんちゃそ</t>
+          <t>茨</t>
         </is>
       </c>
       <c r="G562" t="inlineStr">
         <is>
-          <t>でんちゃそ</t>
+          <t>夏野の茨</t>
         </is>
       </c>
       <c r="H562" t="n">
